--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:27</t>
+    <t xml:space="preserve">2026-09-10 01:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:42</t>
+    <t xml:space="preserve">2026-09-18 11:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:38</t>
+    <t xml:space="preserve">2026-09-23 15:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_o_higgins.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Litueche</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchihue</t>
+    <t xml:space="preserve">Marchigüe</t>
   </si>
   <si>
     <t xml:space="preserve">Navidad</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:44</t>
+    <t xml:space="preserve">2026-10-04 10:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:50</t>
+    <t xml:space="preserve">2026-10-05 16:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1533,7 +1533,7 @@
         <v>96.6</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>102.61</v>
+        <v>102.62</v>
       </c>
       <c r="I34" s="2" t="n">
         <v>63.25</v>
